--- a/sheets/조재수대금교본/검수/히로시의 회상.xlsx
+++ b/sheets/조재수대금교본/검수/히로시의 회상.xlsx
@@ -2997,8 +2997,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I6" s="24"/>
@@ -3009,11 +3008,7 @@
         </is>
       </c>
       <c r="K6" s="24"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="24"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
@@ -3136,37 +3131,17 @@
         </is>
       </c>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
       <c r="F10" s="21"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="24"/>
     </row>
     <row r="11" ht="91.25" customHeight="true">
@@ -3286,8 +3261,7 @@
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="E14" s="24"/>

--- a/sheets/조재수대금교본/검수/히로시의 회상.xlsx
+++ b/sheets/조재수대금교본/검수/히로시의 회상.xlsx
@@ -2839,26 +2839,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="57.14" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="63.76" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="63.76" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2951,7 +2951,7 @@
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="63.76" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="63.76" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="O6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="63.76" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="63.76" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -3084,7 +3084,7 @@
       <c r="N8" s="21"/>
       <c r="O8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="63.76" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="O9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="63.76" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="63.76" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="63.76" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -3207,7 +3207,7 @@
       <c r="N12" s="21"/>
       <c r="O12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="63.76" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="63.76" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="63.76" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="63.76" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -3355,7 +3355,7 @@
       <c r="N16" s="21"/>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="63.76" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -3376,7 +3376,7 @@
       <c r="N17" s="21"/>
       <c r="O17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="63.76" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -3419,6 +3419,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="70"/>
 </worksheet>
 </file>